--- a/outputs/miq-import/miq_nesimi_import_ready.xlsx
+++ b/outputs/miq-import/miq_nesimi_import_ready.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attestasiya_import" sheetId="1" r:id="Rc7d3b6639aad49ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attestasiya_import" sheetId="1" r:id="R9cfe7d1d1c3d49ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -459,16 +459,16 @@
         <x:v>Günay Əhməd-Zadə</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>15.1875</x:v>
+        <x:v>17.25</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>20.25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
         <x:v>6, 42</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>2 sətirin ədədi ortası</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; ədədi orta</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -499,16 +499,16 @@
         <x:v>Günel Məmmədli</x:v>
       </x:c>
       <x:c r="C13" s="10" t="n">
-        <x:v>13.7813</x:v>
+        <x:v>19.03125</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
-        <x:v>18.375</x:v>
+        <x:v>25.375</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>11, 28</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>2 sətirin ədədi ortası</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; ədədi orta</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -794,7 +794,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c1c8362a8614bc8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8efebdd442ca4ada"/>
   </x:tableParts>
 </x:worksheet>
 </file>